--- a/artfynd/A 46059-2021 artfynd.xlsx
+++ b/artfynd/A 46059-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46059-2021 artfynd.xlsx
+++ b/artfynd/A 46059-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98470876</v>
+        <v>98847690</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råningsberget, Lu lm</t>
+          <t>Porsiberget 2, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753269.4959679586</v>
+        <v>753259</v>
       </c>
       <c r="R2" t="n">
-        <v>7384480.068611366</v>
+        <v>7384443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +756,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>lövrik</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98847696</v>
+        <v>98470877</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Porsiberget 1, Lu lm</t>
+          <t>Råningsberget, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753258.8159699106</v>
+        <v>753271</v>
       </c>
       <c r="R3" t="n">
-        <v>7384442.942992621</v>
+        <v>7384485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,91 +878,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>lövrik</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98847689</v>
+        <v>98847839</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porsiberget 4, Lu lm</t>
+          <t>Porsiberget 3, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753258.8159699106</v>
+        <v>753217</v>
       </c>
       <c r="R4" t="n">
-        <v>7384442.942992621</v>
+        <v>7384339</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,27 +965,18 @@
           <t>2021-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-20</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1033,17 +992,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98847690</v>
+        <v>98847696</v>
       </c>
       <c r="B5" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Porsiberget 2, Lu lm</t>
+          <t>Porsiberget 1, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753258.8159699106</v>
+        <v>753259</v>
       </c>
       <c r="R5" t="n">
-        <v>7384442.942992621</v>
+        <v>7384443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,22 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,6 +1139,200 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98470870</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råningsberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>753262</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7384509</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98470876</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Råningsberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>753270</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7384480</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46059-2021 artfynd.xlsx
+++ b/artfynd/A 46059-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98847690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98470877</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98847839</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98847696</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98470870</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,8 +1363,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98470876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>